--- a/信息展示/PC格式.xlsx
+++ b/信息展示/PC格式.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12960"/>
+    <workbookView windowWidth="12900" windowHeight="7035"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,6 +65,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA6A6A6"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>U1 IAP</t>
     </r>
     <r>
@@ -106,6 +113,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA6A6A6"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>U1 IAP</t>
     </r>
     <r>
@@ -137,6 +151,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA6A6A6"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>U1 IAP</t>
     </r>
     <r>
@@ -168,6 +189,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA6A6A6"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>U1 IAP</t>
     </r>
     <r>
@@ -193,6 +221,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA6A6A6"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>U1 IAP</t>
     </r>
     <r>
@@ -221,6 +256,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA6A6A6"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>U1 IAP</t>
     </r>
     <r>
@@ -255,6 +297,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA6A6A6"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>U7 IAP</t>
     </r>
     <r>
@@ -280,6 +329,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>2字节u16：总帧数</t>
     </r>
     <r>
@@ -309,6 +365,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA6A6A6"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>U7 IAP</t>
     </r>
     <r>
@@ -334,6 +397,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA6A6A6"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>U7 IAP</t>
     </r>
     <r>
@@ -359,6 +429,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA6A6A6"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>U7 IAP</t>
     </r>
     <r>
@@ -384,6 +461,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA6A6A6"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>U7 IAP</t>
     </r>
     <r>
@@ -409,6 +493,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA6A6A6"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>U7 IAP</t>
     </r>
     <r>
@@ -440,6 +531,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>固件</t>
     </r>
     <r>
@@ -468,6 +566,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>固件</t>
     </r>
     <r>
@@ -493,6 +598,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>固件</t>
     </r>
     <r>
@@ -518,6 +630,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>固件</t>
     </r>
     <r>
@@ -543,6 +662,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>固件</t>
     </r>
     <r>
@@ -568,6 +694,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>固件</t>
     </r>
     <r>
@@ -601,153 +734,11 @@
     <t>ADC测试结果</t>
   </si>
   <si>
-    <r>
-      <t>1字节u8：VO1 ADC校验是是否通过</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1字节u8：VO2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ADC校验是是否通过</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1字节u8：AMS5600</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ADC校验是是否通过</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1字节u8：VDD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ADC校验是是否通过</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>注：0是不通过，1是通过</t>
-    </r>
+    <t>1字节u8：VO1 ADC校验是是否通过
+1字节u8：VO2  ADC校验是是否通过
+1字节u8：AMS5600  ADC校验是是否通过
+1字节u8：VDD  ADC校验是是否通过
+注：0是不通过，1是通过</t>
   </si>
   <si>
     <t>单帧数据结构 (最低10字节）</t>
@@ -1948,6 +1939,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="26.625" customWidth="1"/>
+    <col min="8" max="8" width="39.625" customWidth="1"/>
     <col min="10" max="10" width="28.125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2697,7 +2689,7 @@
       <c r="I31" s="15"/>
       <c r="J31" s="11"/>
     </row>
-    <row r="32" ht="28" customHeight="1" spans="1:10">
+    <row r="32" ht="180" customHeight="1" spans="1:10">
       <c r="A32" s="1"/>
       <c r="B32" s="24" t="s">
         <v>49</v>
